--- a/dataset/74.xlsx
+++ b/dataset/74.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d85e52ad02e65ccf/Documents/dataset annotation/travel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d85e52ad02e65ccf/Documents/dataset annotation/FILES 1-100/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{9C7A42EB-D08E-4EF9-9A85-8C7779AC78C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C226374-CA24-4054-B8D0-70904463A61C}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{9C7A42EB-D08E-4EF9-9A85-8C7779AC78C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A14C58D4-80BD-4317-BD2F-D06F2701DFD8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F0A3544A-E81D-48A9-AE32-1FC16D9C4A34}"/>
   </bookViews>
   <sheets>
     <sheet name="Backpacking_Thailand_The_Journe" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="173">
   <si>
     <t>start</t>
   </si>
@@ -2700,6 +2711,9 @@
       <c r="C94" t="s">
         <v>94</v>
       </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95">
@@ -2711,6 +2725,9 @@
       <c r="C95" t="s">
         <v>95</v>
       </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96">
@@ -2722,6 +2739,9 @@
       <c r="C96" t="s">
         <v>96</v>
       </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97">
@@ -2733,6 +2753,9 @@
       <c r="C97" t="s">
         <v>97</v>
       </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98">
@@ -2744,6 +2767,9 @@
       <c r="C98" t="s">
         <v>98</v>
       </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99">
@@ -2755,6 +2781,9 @@
       <c r="C99" t="s">
         <v>99</v>
       </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100">
@@ -2766,6 +2795,9 @@
       <c r="C100" t="s">
         <v>100</v>
       </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101">
@@ -2777,6 +2809,9 @@
       <c r="C101" t="s">
         <v>101</v>
       </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102">
@@ -2788,6 +2823,9 @@
       <c r="C102" t="s">
         <v>102</v>
       </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103">
@@ -2799,6 +2837,9 @@
       <c r="C103" t="s">
         <v>103</v>
       </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104">
@@ -2810,6 +2851,9 @@
       <c r="C104" t="s">
         <v>104</v>
       </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105">
@@ -2821,6 +2865,9 @@
       <c r="C105" t="s">
         <v>105</v>
       </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106">
@@ -2831,6 +2878,9 @@
       </c>
       <c r="C106" t="s">
         <v>106</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
